--- a/templates/sanitized/guide-ds-won.xlsx
+++ b/templates/sanitized/guide-ds-won.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">세부내역!$A$1:$O$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">세부내역!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <customWorkbookViews>
     <customWorkbookView name="박수백 - 사용자 보기" guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" tabRatio="823" activeSheetId="1"/>
   </customWorkbookViews>
@@ -3337,9 +3337,8 @@
       <c r="B8" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="44" t="str">
+      <c r="C8" s="44">
         <f>"일금"&amp;NUMBERSTRING(H12,1)&amp;"원정(\"&amp;TEXT(H12,"###,##0")&amp;") V.A.T별도"</f>
-        <v>일금사백삼십구만일천원정(\4,391,000) V.A.T별도</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -3413,11 +3412,9 @@
       </c>
       <c r="G11" s="53">
         <f>세부내역!M27</f>
-        <v>4391729</v>
       </c>
       <c r="H11" s="53">
         <f>F11*G11</f>
-        <v>4391729</v>
       </c>
       <c r="I11" s="46"/>
       <c r="J11" s="2"/>
@@ -3434,7 +3431,6 @@
       <c r="G12" s="196"/>
       <c r="H12" s="196">
         <f>ROUNDDOWN(SUM(H11:H11),-3)</f>
-        <v>4391000</v>
       </c>
       <c r="I12" s="197" t="s">
         <v>42</v>
@@ -3631,9 +3627,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" s="77" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A1" s="247" t="str">
+      <c r="A1" s="247">
         <f>"▣ 공사명 : "&amp;갑지!C5</f>
-        <v>▣ 공사명 : 설치 or 공사 끝맺음</v>
       </c>
       <c r="B1" s="247"/>
       <c r="C1" s="247"/>
@@ -4045,27 +4040,13 @@
       <c r="E6" s="149"/>
       <c r="F6" s="150"/>
       <c r="G6" s="151"/>
-      <c r="H6" s="152">
-        <f t="shared" ref="H6:H14" si="0">F6*G6</f>
-      </c>
-      <c r="I6" s="153">
-        <f t="shared" ref="I6" si="1">G6*1.2</f>
-      </c>
-      <c r="J6" s="147">
-        <f t="shared" ref="J6" si="2">I6*F6</f>
-      </c>
-      <c r="K6" s="147">
-        <f t="shared" ref="K6" si="3">INT(SUM((U6*V6),V6)*T6)</f>
-      </c>
-      <c r="L6" s="149">
-        <f t="shared" ref="L6" si="4">F6*K6</f>
-      </c>
-      <c r="M6" s="147">
-        <f t="shared" ref="M6" si="5">L6+J6</f>
-      </c>
-      <c r="N6" s="186">
-        <f t="shared" ref="N6:N14" si="6">IFERROR((I6/G6)-1,"-")</f>
-      </c>
+      <c r="H6" s="152"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="147"/>
+      <c r="K6" s="147"/>
+      <c r="L6" s="149"/>
+      <c r="M6" s="147"/>
+      <c r="N6" s="186"/>
       <c r="O6" s="154"/>
       <c r="P6" s="167"/>
       <c r="Q6" s="164"/>
@@ -4073,111 +4054,57 @@
       <c r="S6" s="155"/>
       <c r="T6" s="156"/>
       <c r="U6" s="157"/>
-      <c r="V6" s="158">
-        <f t="shared" ref="V6" si="7">SUM(X6,Z6,AB6,AD6,AF6,AH6,AJ6,AL6,AN6,AP6,AR6,AT6,AV6,AX6,AZ6,BB6,BD6)</f>
-      </c>
-      <c r="W6" s="159">
-        <f t="shared" ref="W6" si="8">0.7+0.59</f>
-      </c>
-      <c r="X6" s="158">
-        <f t="shared" ref="X6" si="9">W6*X$3</f>
-      </c>
-      <c r="Y6" s="159">
-        <f t="shared" ref="Y6" si="10">0.5+0.3+0.7+0.89</f>
-      </c>
-      <c r="Z6" s="158">
-        <f t="shared" ref="Z6" si="11">Y6*Z$3</f>
-      </c>
+      <c r="V6" s="158"/>
+      <c r="W6" s="159"/>
+      <c r="X6" s="158"/>
+      <c r="Y6" s="159"/>
+      <c r="Z6" s="158"/>
       <c r="AA6" s="159"/>
-      <c r="AB6" s="158">
-        <f t="shared" ref="AB6" si="12">AA6*AB$3</f>
-      </c>
+      <c r="AB6" s="158"/>
       <c r="AC6" s="159"/>
-      <c r="AD6" s="158">
-        <f t="shared" ref="AD6" si="13">AC6*AD$3</f>
-      </c>
+      <c r="AD6" s="158"/>
       <c r="AE6" s="160"/>
-      <c r="AF6" s="158">
-        <f t="shared" ref="AF6" si="14">AE6*AF$3</f>
-      </c>
+      <c r="AF6" s="158"/>
       <c r="AG6" s="161"/>
-      <c r="AH6" s="158">
-        <f t="shared" ref="AH6" si="15">AG6*AH$3</f>
-      </c>
+      <c r="AH6" s="158"/>
       <c r="AI6" s="161"/>
-      <c r="AJ6" s="158">
-        <f t="shared" ref="AJ6" si="16">AI6*AJ$3</f>
-      </c>
+      <c r="AJ6" s="158"/>
       <c r="AK6" s="161"/>
-      <c r="AL6" s="158">
-        <f t="shared" ref="AL6" si="17">AK6*AL$3</f>
-      </c>
+      <c r="AL6" s="158"/>
       <c r="AM6" s="161"/>
-      <c r="AN6" s="158">
-        <f t="shared" ref="AN6" si="18">AM6*AN$3</f>
-      </c>
+      <c r="AN6" s="158"/>
       <c r="AO6" s="161"/>
-      <c r="AP6" s="158">
-        <f t="shared" ref="AP6" si="19">AO6*AP$3</f>
-      </c>
+      <c r="AP6" s="158"/>
       <c r="AQ6" s="161"/>
-      <c r="AR6" s="158">
-        <f t="shared" ref="AR6" si="20">AQ6*AR$3</f>
-      </c>
+      <c r="AR6" s="158"/>
       <c r="AS6" s="161"/>
-      <c r="AT6" s="158">
-        <f t="shared" ref="AT6" si="21">AS6*AT$3</f>
-      </c>
+      <c r="AT6" s="158"/>
       <c r="AU6" s="161"/>
-      <c r="AV6" s="158">
-        <f t="shared" ref="AV6" si="22">AU6*AV$3</f>
-      </c>
+      <c r="AV6" s="158"/>
       <c r="AW6" s="161"/>
-      <c r="AX6" s="158">
-        <f t="shared" ref="AX6" si="23">AW6*AX$3</f>
-      </c>
+      <c r="AX6" s="158"/>
       <c r="AY6" s="161"/>
-      <c r="AZ6" s="158">
-        <f t="shared" ref="AZ6" si="24">AY6*AZ$3</f>
-      </c>
+      <c r="AZ6" s="158"/>
       <c r="BA6" s="160"/>
-      <c r="BB6" s="158">
-        <f t="shared" ref="BB6" si="25">BA6*BB$3</f>
-      </c>
+      <c r="BB6" s="158"/>
       <c r="BC6" s="162"/>
-      <c r="BD6" s="158">
-        <f t="shared" ref="BD6" si="26">BC6*BD$3</f>
-      </c>
+      <c r="BD6" s="158"/>
     </row>
     <row r="7" spans="1:56" ht="21" customHeight="1">
-      <c r="A7" s="82">
-        <f>A6+1</f>
-      </c>
+      <c r="A7" s="82"/>
       <c r="B7" s="26"/>
       <c r="C7" s="76"/>
       <c r="D7" s="138"/>
       <c r="E7" s="59"/>
-      <c r="F7" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F7" s="57"/>
       <c r="G7" s="131"/>
-      <c r="H7" s="131">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H7" s="131"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="22">
-        <f t="shared" ref="J7:J14" si="27">I7*F7</f>
-      </c>
+      <c r="J7" s="22"/>
       <c r="K7" s="22"/>
-      <c r="L7" s="58">
-        <f t="shared" ref="L7:L14" si="28">F7*K7</f>
-      </c>
-      <c r="M7" s="22">
-        <f t="shared" ref="M7" si="29">+J7+L7</f>
-      </c>
-      <c r="N7" s="186">
-        <f t="shared" si="6"/>
-      </c>
+      <c r="L7" s="58"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="186"/>
       <c r="O7" s="103"/>
       <c r="P7" s="176"/>
       <c r="Q7" s="172"/>
@@ -4221,34 +4148,20 @@
       <c r="BD7" s="172"/>
     </row>
     <row r="8" spans="1:56" ht="21" customHeight="1">
-      <c r="A8" s="82">
-        <f t="shared" ref="A8:A14" si="30">A7+1</f>
-      </c>
+      <c r="A8" s="82"/>
       <c r="B8" s="26"/>
       <c r="C8" s="76"/>
       <c r="D8" s="138"/>
       <c r="E8" s="59"/>
-      <c r="F8" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F8" s="57"/>
       <c r="G8" s="131"/>
-      <c r="H8" s="131">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H8" s="131"/>
       <c r="I8" s="23"/>
-      <c r="J8" s="22">
-        <f t="shared" si="27"/>
-      </c>
+      <c r="J8" s="22"/>
       <c r="K8" s="22"/>
-      <c r="L8" s="58">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="M8" s="22">
-        <f t="shared" ref="M8:M14" si="31">+J8+L8</f>
-      </c>
-      <c r="N8" s="186">
-        <f t="shared" si="6"/>
-      </c>
+      <c r="L8" s="58"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="186"/>
       <c r="O8" s="103"/>
       <c r="P8" s="176"/>
       <c r="Q8" s="172"/>
@@ -4292,34 +4205,20 @@
       <c r="BD8" s="172"/>
     </row>
     <row r="9" spans="1:56" ht="21" customHeight="1">
-      <c r="A9" s="82">
-        <f t="shared" si="30"/>
-      </c>
+      <c r="A9" s="82"/>
       <c r="B9" s="56"/>
       <c r="C9" s="76"/>
       <c r="D9" s="138"/>
       <c r="E9" s="59"/>
-      <c r="F9" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F9" s="57"/>
       <c r="G9" s="131"/>
-      <c r="H9" s="131">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H9" s="131"/>
       <c r="I9" s="22"/>
-      <c r="J9" s="22">
-        <f t="shared" si="27"/>
-      </c>
+      <c r="J9" s="22"/>
       <c r="K9" s="22"/>
-      <c r="L9" s="58">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="M9" s="22">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="N9" s="186">
-        <f t="shared" si="6"/>
-      </c>
+      <c r="L9" s="58"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="186"/>
       <c r="O9" s="116"/>
       <c r="P9" s="176"/>
       <c r="Q9" s="172"/>
@@ -4363,34 +4262,20 @@
       <c r="BD9" s="172"/>
     </row>
     <row r="10" spans="1:56" ht="21" customHeight="1">
-      <c r="A10" s="82">
-        <f t="shared" si="30"/>
-      </c>
+      <c r="A10" s="82"/>
       <c r="B10" s="76"/>
       <c r="C10" s="80"/>
       <c r="D10" s="139"/>
       <c r="E10" s="55"/>
-      <c r="F10" s="61">
-        <f>F6</f>
-      </c>
+      <c r="F10" s="61"/>
       <c r="G10" s="131"/>
-      <c r="H10" s="131">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H10" s="131"/>
       <c r="I10" s="22"/>
-      <c r="J10" s="22">
-        <f t="shared" si="27"/>
-      </c>
+      <c r="J10" s="22"/>
       <c r="K10" s="22"/>
-      <c r="L10" s="58">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="M10" s="22">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="N10" s="186">
-        <f t="shared" si="6"/>
-      </c>
+      <c r="L10" s="58"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="186"/>
       <c r="O10" s="116"/>
       <c r="P10" s="177"/>
       <c r="Q10" s="172"/>
@@ -4434,34 +4319,20 @@
       <c r="BD10" s="172"/>
     </row>
     <row r="11" spans="1:56" ht="21" customHeight="1">
-      <c r="A11" s="82">
-        <f t="shared" si="30"/>
-      </c>
+      <c r="A11" s="82"/>
       <c r="B11" s="56"/>
       <c r="C11" s="62"/>
       <c r="D11" s="140"/>
       <c r="E11" s="58"/>
-      <c r="F11" s="57">
-        <f>F6</f>
-      </c>
+      <c r="F11" s="57"/>
       <c r="G11" s="131"/>
-      <c r="H11" s="131">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H11" s="131"/>
       <c r="I11" s="22"/>
-      <c r="J11" s="22">
-        <f t="shared" si="27"/>
-      </c>
+      <c r="J11" s="22"/>
       <c r="K11" s="22"/>
-      <c r="L11" s="58">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="M11" s="22">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="N11" s="186">
-        <f t="shared" si="6"/>
-      </c>
+      <c r="L11" s="58"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="186"/>
       <c r="O11" s="116"/>
       <c r="P11" s="178"/>
       <c r="Q11" s="172"/>
@@ -4505,34 +4376,20 @@
       <c r="BD11" s="172"/>
     </row>
     <row r="12" spans="1:56" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="82">
-        <f t="shared" si="30"/>
-      </c>
+      <c r="A12" s="82"/>
       <c r="B12" s="73"/>
       <c r="C12" s="105"/>
       <c r="D12" s="141"/>
       <c r="E12" s="81"/>
-      <c r="F12" s="61">
-        <f>F6*2</f>
-      </c>
+      <c r="F12" s="61"/>
       <c r="G12" s="131"/>
-      <c r="H12" s="131">
-        <f t="shared" si="0"/>
-      </c>
+      <c r="H12" s="131"/>
       <c r="I12" s="23"/>
-      <c r="J12" s="22">
-        <f t="shared" si="27"/>
-      </c>
+      <c r="J12" s="22"/>
       <c r="K12" s="22"/>
-      <c r="L12" s="58">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="M12" s="22">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="N12" s="186">
-        <f t="shared" si="6"/>
-      </c>
+      <c r="L12" s="58"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="186"/>
       <c r="O12" s="117"/>
       <c r="P12" s="179"/>
       <c r="Q12" s="173"/>
@@ -4577,8 +4434,7 @@
     </row>
     <row r="13" spans="1:56" s="28" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="82">
-        <f t="shared" si="30"/>
-        <v>8</v>
+        <f>A12+1</f>
       </c>
       <c r="B13" s="73" t="s">
         <v>30</v>
@@ -4595,32 +4451,25 @@
       </c>
       <c r="G13" s="129">
         <f>H12*40%</f>
-        <v>4800</v>
       </c>
       <c r="H13" s="131">
-        <f t="shared" si="0"/>
-        <v>4800</v>
+        <f>F13*G13</f>
       </c>
       <c r="I13" s="55">
         <f>J12*40%</f>
-        <v>4800</v>
       </c>
       <c r="J13" s="22">
-        <f t="shared" si="27"/>
-        <v>4800</v>
+        <f>I13*F13</f>
       </c>
       <c r="K13" s="22"/>
       <c r="L13" s="58">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>F13*K13</f>
       </c>
       <c r="M13" s="22">
-        <f t="shared" si="31"/>
-        <v>4800</v>
+        <f>+J13+L13</f>
       </c>
       <c r="N13" s="186">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>IFERROR((I13/G13)-1,"-")</f>
       </c>
       <c r="O13" s="116"/>
       <c r="P13" s="179"/>
@@ -4666,8 +4515,7 @@
     </row>
     <row r="14" spans="1:56" ht="21" customHeight="1">
       <c r="A14" s="109">
-        <f t="shared" si="30"/>
-        <v>9</v>
+        <f>A13+1</f>
       </c>
       <c r="B14" s="71" t="s">
         <v>21</v>
@@ -4684,32 +4532,25 @@
       </c>
       <c r="G14" s="184">
         <f>INT(SUM(H6:H13)*2%)</f>
-        <v>58336</v>
       </c>
       <c r="H14" s="132">
-        <f t="shared" si="0"/>
-        <v>58336</v>
+        <f>F14*G14</f>
       </c>
       <c r="I14" s="102">
         <f>INT(SUM(J6:J13)*2%)</f>
-        <v>69936</v>
       </c>
       <c r="J14" s="27">
-        <f t="shared" si="27"/>
-        <v>69936</v>
+        <f>I14*F14</f>
       </c>
       <c r="K14" s="27"/>
       <c r="L14" s="63">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f>F14*K14</f>
       </c>
       <c r="M14" s="27">
-        <f t="shared" si="31"/>
-        <v>69936</v>
+        <f>+J14+L14</f>
       </c>
       <c r="N14" s="187">
-        <f t="shared" si="6"/>
-        <v>0.19884805266044991</v>
+        <f>IFERROR((I14/G14)-1,"-")</f>
       </c>
       <c r="O14" s="115"/>
       <c r="P14" s="180"/>
@@ -4765,25 +4606,20 @@
       <c r="G15" s="214"/>
       <c r="H15" s="214">
         <f>SUM(H6:H14)</f>
-        <v>2975136</v>
       </c>
       <c r="I15" s="215"/>
       <c r="J15" s="215">
         <f>SUM(J6:J14)</f>
-        <v>3566736</v>
       </c>
       <c r="K15" s="215"/>
       <c r="L15" s="215">
         <f>SUM(L6:L14)</f>
-        <v>288221</v>
       </c>
       <c r="M15" s="215">
         <f>SUM(M6:M14)</f>
-        <v>3854957</v>
       </c>
       <c r="N15" s="216">
         <f>AVERAGE(N6:N14)</f>
-        <v>9.9712013165112467E-2</v>
       </c>
       <c r="O15" s="217"/>
       <c r="P15" s="100"/>
@@ -4835,7 +4671,6 @@
       <c r="L17" s="25"/>
       <c r="M17" s="25">
         <f>INT(L15*F17)</f>
-        <v>14007</v>
       </c>
       <c r="N17" s="133"/>
       <c r="O17" s="93"/>
@@ -4866,7 +4701,6 @@
       <c r="L18" s="25"/>
       <c r="M18" s="25">
         <f>INT(L15*F18)</f>
-        <v>1222</v>
       </c>
       <c r="N18" s="133"/>
       <c r="O18" s="93"/>
@@ -4897,7 +4731,6 @@
       <c r="L19" s="25"/>
       <c r="M19" s="25">
         <f>INT(L15*F19)</f>
-        <v>2769</v>
       </c>
       <c r="N19" s="133"/>
       <c r="O19" s="93"/>
@@ -5024,7 +4857,6 @@
       <c r="L23" s="25"/>
       <c r="M23" s="189">
         <f>INT(M15*F23)</f>
-        <v>119889</v>
       </c>
       <c r="N23" s="134"/>
       <c r="O23" s="106"/>
@@ -5087,7 +4919,6 @@
       <c r="L25" s="42"/>
       <c r="M25" s="27">
         <f>INT((SUM(M15,M23,M17))*F25)</f>
-        <v>398885</v>
       </c>
       <c r="N25" s="135"/>
       <c r="O25" s="118"/>
@@ -5110,7 +4941,6 @@
       <c r="L26" s="208"/>
       <c r="M26" s="209">
         <f>SUM(M17:M25)</f>
-        <v>536772</v>
       </c>
       <c r="N26" s="207"/>
       <c r="O26" s="210"/>
@@ -5133,7 +4963,6 @@
       <c r="L27" s="198"/>
       <c r="M27" s="202">
         <f>M15+M26</f>
-        <v>4391729</v>
       </c>
       <c r="N27" s="201"/>
       <c r="O27" s="203"/>

--- a/templates/sanitized/guide-ds-won.xlsx
+++ b/templates/sanitized/guide-ds-won.xlsx
@@ -3570,16 +3570,6 @@
     </row>
     <row r="22" spans="1:14" ht="10.3" customHeight="1"/>
   </sheetData>
-  <customSheetViews>
-    <customSheetView guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview">
-      <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-      <printOptions horizontalCentered="1"/>
-      <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-      <headerFooter scaleWithDoc="0">
-        <oddFooter>&amp;C&amp;P / &amp;N&amp;R㈜서울영상테크</oddFooter>
-      </headerFooter>
-    </customSheetView>
-  </customSheetViews>
   <mergeCells count="5">
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B19:B20"/>
@@ -5367,18 +5357,6 @@
     <row r="420" ht="21" customHeight="1"/>
     <row r="421" ht="21" customHeight="1"/>
   </sheetData>
-  <customSheetViews>
-    <customSheetView guid="{1FA04683-E8B6-40FB-A56A-4A427B1A01C5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview">
-      <pane xSplit="5" ySplit="3" topLeftCell="F4" activePane="bottomRight" state="frozen"/>
-      <selection pane="bottomRight" activeCell="B16" sqref="B16"/>
-      <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.51181102362204722" header="0.31496062992125984" footer="0.31496062992125984"/>
-      <printOptions horizontalCentered="1"/>
-      <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape"/>
-      <headerFooter scaleWithDoc="0">
-        <oddFooter>&amp;C&amp;P / &amp;N&amp;R㈜서울영상테크</oddFooter>
-      </headerFooter>
-    </customSheetView>
-  </customSheetViews>
   <mergeCells count="37">
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A26:C26"/>
